--- a/data/trans_orig/P1435_2011_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1435_2011_2023-Edad-trans_orig.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>449366</t>
+          <t>449179</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>415807</t>
+          <t>416811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>427149</t>
+          <t>427236</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>869231</t>
+          <t>869141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>880467</t>
+          <t>880409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>13419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680527</t>
+          <t>680850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>584172</t>
+          <t>586316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>601449</t>
+          <t>601898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270324</t>
+          <t>1269080</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287220</t>
+          <t>1287720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>23939</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>680018</t>
+          <t>679383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>698613</t>
+          <t>697785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1361110</t>
+          <t>1361828</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1379864</t>
+          <t>1380959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>31467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12848</t>
+          <t>11753</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>604517</t>
+          <t>604604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>613624</t>
+          <t>613633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>564593</t>
+          <t>566022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>590464</t>
+          <t>591204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1172319</t>
+          <t>1173451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1201468</t>
+          <t>1201624</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25735</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>420955</t>
+          <t>420367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>428388</t>
+          <t>428391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>401069</t>
+          <t>400193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>425098</t>
+          <t>423683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>826896</t>
+          <t>825471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>852505</t>
+          <t>851225</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46731</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>51758</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>335113</t>
+          <t>336079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>348079</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>644250</t>
+          <t>643767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>657889</t>
+          <t>657917</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3159,12 +3159,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>244588</t>
+          <t>243754</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>379255</t>
+          <t>377996</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>387985</t>
+          <t>387994</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3517,12 +3517,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>627285</t>
+          <t>627606</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>637740</t>
+          <t>637517</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3407438</t>
+          <t>3407724</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3420946</t>
+          <t>3420866</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3407965</t>
+          <t>3406722</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3453096</t>
+          <t>3451374</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6823216</t>
+          <t>6822437</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6870768</t>
+          <t>6870771</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>105213</t>
+          <t>106935</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>150344</t>
+          <t>151587</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>114320</t>
+          <t>114317</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>161872</t>
+          <t>162651</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4757,32 +4757,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>35475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4792,32 +4792,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11337</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -4835,27 +4835,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>394338</t>
+          <t>402667</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>377190</t>
+          <t>383741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4870,32 +4870,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>297307</t>
+          <t>344432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>282727</t>
+          <t>327037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305950</t>
+          <t>353130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4905,32 +4905,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>691644</t>
+          <t>747099</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>673300</t>
+          <t>728103</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>701850</t>
+          <t>759304</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4983,17 +4983,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5178,32 +5178,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32769</t>
+          <t>34534</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5248,32 +5248,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>27536</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>38743</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5291,32 +5291,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>418837</t>
+          <t>472597</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>411103</t>
+          <t>464374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>422039</t>
+          <t>475656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>490591</t>
+          <t>477840</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>478735</t>
+          <t>466549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>485839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>909428</t>
+          <t>950437</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>896308</t>
+          <t>938232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>918935</t>
+          <t>960822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5404,17 +5404,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5439,17 +5439,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5474,17 +5474,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5634,32 +5634,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5669,32 +5669,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34236</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25790</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43350</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5704,32 +5704,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>45743</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>34367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>58280</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5747,32 +5747,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>529978</t>
+          <t>613909</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>523098</t>
+          <t>606651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533454</t>
+          <t>618501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5782,32 +5782,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>506824</t>
+          <t>581863</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497710</t>
+          <t>571991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>515270</t>
+          <t>591721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5817,32 +5817,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1036803</t>
+          <t>1195772</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1024302</t>
+          <t>1183235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1045723</t>
+          <t>1207148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -5860,17 +5860,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5895,17 +5895,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>541060</t>
+          <t>620678</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5930,17 +5930,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1077399</t>
+          <t>1241515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6090,32 +6090,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15284</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6125,32 +6125,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68793</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54610</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86493</t>
+          <t>82526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6160,32 +6160,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>84077</t>
+          <t>84529</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47829</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108886</t>
+          <t>101234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -6203,32 +6203,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>871427</t>
+          <t>683417</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>859591</t>
+          <t>673810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>881128</t>
+          <t>690143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6238,32 +6238,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>643705</t>
+          <t>668068</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626005</t>
+          <t>653969</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657888</t>
+          <t>679644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6273,32 +6273,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1515132</t>
+          <t>1351486</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1490323</t>
+          <t>1334781</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1551380</t>
+          <t>1364855</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -6316,17 +6316,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6351,17 +6351,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6386,17 +6386,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1599209</t>
+          <t>1436015</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1599209</t>
+          <t>1436015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1599209</t>
+          <t>1436015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6546,32 +6546,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6581,32 +6581,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79946</t>
+          <t>92240</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68666</t>
+          <t>79051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92798</t>
+          <t>107210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6616,32 +6616,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>89790</t>
+          <t>103646</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>76316</t>
+          <t>89163</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104666</t>
+          <t>119013</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -6659,32 +6659,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>550393</t>
+          <t>596954</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>543403</t>
+          <t>590336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>555211</t>
+          <t>602270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6694,32 +6694,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>463343</t>
+          <t>512392</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>450491</t>
+          <t>497422</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>474623</t>
+          <t>525581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6729,32 +6729,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1013736</t>
+          <t>1109345</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>998860</t>
+          <t>1093978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1027210</t>
+          <t>1123828</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -6772,17 +6772,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6807,17 +6807,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>543289</t>
+          <t>604632</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>543289</t>
+          <t>604632</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>543289</t>
+          <t>604632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6842,17 +6842,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1103526</t>
+          <t>1212991</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1103526</t>
+          <t>1212991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1103526</t>
+          <t>1212991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7002,32 +7002,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7037,32 +7037,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>251754</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>43571</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>467461</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7072,32 +7072,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67055</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613892</t>
+          <t>76622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -7115,32 +7115,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>357441</t>
+          <t>395427</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351180</t>
+          <t>389097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>361664</t>
+          <t>400387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7150,32 +7150,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>356256</t>
+          <t>385758</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140549</t>
+          <t>375352</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>541509</t>
+          <t>395216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7185,32 +7185,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>713696</t>
+          <t>781186</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>361565</t>
+          <t>768377</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>908402</t>
+          <t>791945</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -7228,17 +7228,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>608010</t>
+          <t>438787</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>975457</t>
+          <t>844999</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>975457</t>
+          <t>844999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>975457</t>
+          <t>844999</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7458,32 +7458,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7493,32 +7493,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>39905</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28620</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45993</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7528,32 +7528,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32938</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>51604</t>
+          <t>55272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -7571,32 +7571,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>278035</t>
+          <t>305262</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>273682</t>
+          <t>300712</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>280518</t>
+          <t>308038</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7606,32 +7606,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>389798</t>
+          <t>424704</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>379838</t>
+          <t>414088</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>397211</t>
+          <t>433329</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7641,32 +7641,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>667832</t>
+          <t>729966</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>719535</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>675652</t>
+          <t>739804</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -7684,17 +7684,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7914,27 +7914,27 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>56578</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -7949,32 +7949,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>507569</t>
+          <t>333739</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>310448</t>
+          <t>307501</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1046860</t>
+          <t>364220</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>564146</t>
+          <t>393314</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>358827</t>
+          <t>358755</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1338126</t>
+          <t>430079</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -8027,22 +8027,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>3400448</t>
+          <t>3470234</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>3381644</t>
+          <t>3452952</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3417196</t>
+          <t>3485203</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8062,32 +8062,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3147824</t>
+          <t>3395057</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2608533</t>
+          <t>3364576</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3344945</t>
+          <t>3421295</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8097,32 +8097,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>6548273</t>
+          <t>6865290</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5774293</t>
+          <t>6828525</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6753592</t>
+          <t>6899849</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -8140,17 +8140,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3457026</t>
+          <t>3529808</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8175,17 +8175,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3655393</t>
+          <t>3728796</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8210,17 +8210,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7112419</t>
+          <t>7258604</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
